--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Pharma Healthcare and Diagnostics (P.H.D) Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Pharma Healthcare and Diagnostics (P.H.D) Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="124">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Pharma Healthcare and Diagnostics (P.H.D) Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,145 +70,217 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Divi's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE361B01024</t>
+  </si>
+  <si>
     <t>Cipla Ltd.</t>
   </si>
   <si>
     <t>INE059A01026</t>
   </si>
   <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Divi's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE361B01024</t>
-  </si>
-  <si>
     <t>Aurobindo Pharma Ltd.</t>
   </si>
   <si>
     <t>INE406A01037</t>
   </si>
   <si>
+    <t>Alkem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE540L01014</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
     <t>Lupin Ltd.</t>
   </si>
   <si>
     <t>INE326A01037</t>
   </si>
   <si>
-    <t>Alkem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE540L01014</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
     <t>Gland Pharma Ltd.</t>
   </si>
   <si>
     <t>INE068V01023</t>
   </si>
   <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Pfizer Ltd.</t>
+  </si>
+  <si>
+    <t>INE182A01018</t>
+  </si>
+  <si>
+    <t>Alembic Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE901L01018</t>
+  </si>
+  <si>
+    <t>Apollo Hospitals Enterprise Ltd.</t>
+  </si>
+  <si>
+    <t>INE437A01024</t>
+  </si>
+  <si>
+    <t>Medplus Health Services Ltd</t>
+  </si>
+  <si>
+    <t>INE804L01022</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
     <t>Mankind Pharma Ltd</t>
   </si>
   <si>
     <t>INE634S01028</t>
   </si>
   <si>
-    <t>Apollo Hospitals Enterprise Ltd.</t>
-  </si>
-  <si>
-    <t>INE437A01024</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Pfizer Ltd.</t>
-  </si>
-  <si>
-    <t>INE182A01018</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
+    <t>Biocon Ltd.</t>
+  </si>
+  <si>
+    <t>INE376G01013</t>
+  </si>
+  <si>
+    <t>Shilpa Medicare Ltd.</t>
+  </si>
+  <si>
+    <t>INE790G01031</t>
+  </si>
+  <si>
+    <t>Sagility India Ltd</t>
+  </si>
+  <si>
+    <t>INE0W2G01015</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>Thyrocare Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE594H01019</t>
+  </si>
+  <si>
+    <t>Advanced Enzyme Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE837H01020</t>
+  </si>
+  <si>
+    <t>Windlas Biotech Ltd.</t>
+  </si>
+  <si>
+    <t>INE0H5O01029</t>
+  </si>
+  <si>
+    <t>Medi Assist Healthcare Services Ltd</t>
+  </si>
+  <si>
+    <t>INE456Z01021</t>
   </si>
   <si>
     <t>Insurance</t>
   </si>
   <si>
+    <t>Aarti Drugs Ltd.</t>
+  </si>
+  <si>
+    <t>INE767A01016</t>
+  </si>
+  <si>
+    <t>Fine Organic Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE686Y01026</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Sun Pharma Advanced Research Co. Ltd</t>
+  </si>
+  <si>
+    <t>INE232I01014</t>
+  </si>
+  <si>
+    <t>Yatharth Hospital &amp; Trauma Care Services Pvt Ltd</t>
+  </si>
+  <si>
+    <t>INE0JO301016</t>
+  </si>
+  <si>
+    <t>Sanofi Consumer Healthcare India Ltd</t>
+  </si>
+  <si>
+    <t>INE0UOS01011</t>
+  </si>
+  <si>
+    <t>Glenmark Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE935A01035</t>
+  </si>
+  <si>
+    <t>Aarti Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE769A01020</t>
+  </si>
+  <si>
+    <t>FDC Ltd.</t>
+  </si>
+  <si>
+    <t>INE258B01022</t>
+  </si>
+  <si>
+    <t>Procter &amp; Gamble Health Ltd.</t>
+  </si>
+  <si>
+    <t>INE199A01012</t>
+  </si>
+  <si>
     <t>Astrazeneca Pharma India Ltd.</t>
   </si>
   <si>
     <t>INE203A01020</t>
   </si>
   <si>
-    <t>Biocon Ltd.</t>
-  </si>
-  <si>
-    <t>INE376G01013</t>
-  </si>
-  <si>
-    <t>Windlas Biotech Ltd.</t>
-  </si>
-  <si>
-    <t>INE0H5O01029</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Medi Assist Healthcare Services Ltd</t>
-  </si>
-  <si>
-    <t>INE456Z01021</t>
-  </si>
-  <si>
-    <t>Medplus Health Services Ltd</t>
-  </si>
-  <si>
-    <t>INE804L01022</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Advanced Enzyme Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE837H01020</t>
-  </si>
-  <si>
-    <t>Shilpa Medicare Ltd.</t>
-  </si>
-  <si>
-    <t>INE790G01031</t>
-  </si>
-  <si>
-    <t>Alembic Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE901L01018</t>
-  </si>
-  <si>
-    <t>Thyrocare Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE594H01019</t>
+    <t>Emcure Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE168P01015</t>
   </si>
   <si>
     <t>Senores Pharmaceuticals Ltd</t>
@@ -217,106 +289,10 @@
     <t>INE0RB801010</t>
   </si>
   <si>
-    <t>Pharmaceuticals, Biotechnology</t>
-  </si>
-  <si>
-    <t>FDC Ltd.</t>
-  </si>
-  <si>
-    <t>INE258B01022</t>
-  </si>
-  <si>
-    <t>Fine Organic Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE686Y01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Glenmark Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE935A01035</t>
-  </si>
-  <si>
-    <t>Aarti Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE769A01020</t>
-  </si>
-  <si>
-    <t>Aarti Drugs Ltd.</t>
-  </si>
-  <si>
-    <t>INE767A01016</t>
-  </si>
-  <si>
-    <t>Atul Ltd.</t>
-  </si>
-  <si>
-    <t>INE100A01010</t>
-  </si>
-  <si>
-    <t>Blue Jet Healthcare Ltd.</t>
-  </si>
-  <si>
-    <t>INE0KBH01020</t>
-  </si>
-  <si>
-    <t>Yatharth Hospital &amp; Trauma Care Services Pvt Ltd</t>
-  </si>
-  <si>
-    <t>INE0JO301016</t>
-  </si>
-  <si>
-    <t>Fortis Healthcare Ltd.</t>
-  </si>
-  <si>
-    <t>INE061F01013</t>
-  </si>
-  <si>
-    <t>Sanofi Consumer Healthcare India Ltd</t>
-  </si>
-  <si>
-    <t>INE0UOS01011</t>
-  </si>
-  <si>
-    <t>Procter &amp; Gamble Health Ltd.</t>
-  </si>
-  <si>
-    <t>INE199A01012</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Emcure Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE168P01015</t>
-  </si>
-  <si>
-    <t>Alivus Life Sciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE03Q201024</t>
-  </si>
-  <si>
-    <t>Sun Pharma Advanced Research Co. Ltd</t>
-  </si>
-  <si>
-    <t>INE232I01014</t>
-  </si>
-  <si>
-    <t>Aster DM Healthcare Ltd.</t>
-  </si>
-  <si>
-    <t>INE914M01019</t>
+    <t>Unichem Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE351A01035</t>
   </si>
   <si>
     <t>Laxmi Dental Ltd.</t>
@@ -328,24 +304,6 @@
     <t>Healthcare Equipment &amp; Supplies</t>
   </si>
   <si>
-    <t>Unichem Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE351A01035</t>
-  </si>
-  <si>
-    <t>Vinati Organics Ltd.</t>
-  </si>
-  <si>
-    <t>INE410B01037</t>
-  </si>
-  <si>
-    <t>Galaxy Surfactants Ltd.</t>
-  </si>
-  <si>
-    <t>INE600K01018</t>
-  </si>
-  <si>
     <t>Laxmi Organic Industries Ltd.</t>
   </si>
   <si>
@@ -415,7 +373,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -427,7 +385,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t xml:space="preserve">Benchmark name - BSE Healthcare TRI </t>
+    <t>Benchmark name - S&amp;P BSE Healthcare TRI</t>
   </si>
 </sst>
 </file>
@@ -798,13 +756,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -822,7 +780,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="19126200"/>
+          <a:off x="666750" y="17792700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -837,13 +795,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -861,7 +819,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="21983700"/>
+          <a:off x="666750" y="20650200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1195,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J112"/>
+  <dimension ref="B1:J105"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1203,7 +1161,7 @@
     <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="17.0" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="34.57142857142857" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="10.857142857142858" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
@@ -1295,10 +1253,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>485841.64999999997</v>
+        <v>534162.88</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9879223372824999</v>
+        <v>0.9698786231990001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1332,10 +1290,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>485841.64999999997</v>
+        <v>534162.88</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9879223372824999</v>
+        <v>0.9698786231990001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1358,13 +1316,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>3824250</v>
+        <v>4156644</v>
       </c>
       <c r="G8" s="15">
-        <v>66693.01</v>
+        <v>69731.86</v>
       </c>
       <c r="H8" s="16">
-        <v>0.1356152036774</v>
+        <v>0.1266120183604</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1387,13 +1345,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>3228454</v>
+        <v>4250104</v>
       </c>
       <c r="G9" s="15">
-        <v>47761.75</v>
+        <v>53177.30</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0971199148792</v>
+        <v>0.0965539322192</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1416,13 +1374,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>3345560</v>
+        <v>752472</v>
       </c>
       <c r="G10" s="15">
-        <v>40727.17</v>
+        <v>49753.45</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0828156272262</v>
+        <v>0.0903372536584</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1445,13 +1403,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>533357</v>
+        <v>2948259</v>
       </c>
       <c r="G11" s="15">
-        <v>29749.05</v>
+        <v>43212.63</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0604924485333</v>
+        <v>0.0784610980255</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1474,13 +1432,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>2044911</v>
+        <v>3040471</v>
       </c>
       <c r="G12" s="15">
-        <v>23964.31</v>
+        <v>34898.53</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0487296162167</v>
+        <v>0.0633652009441</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1503,13 +1461,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>1055581</v>
+        <v>445422</v>
       </c>
       <c r="G13" s="15">
-        <v>21960.83</v>
+        <v>22709.84</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0446556908044</v>
+        <v>0.0412342174587</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1532,13 +1490,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>376033</v>
+        <v>2375809</v>
       </c>
       <c r="G14" s="15">
-        <v>19038.74</v>
+        <v>22095.02</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0387138412685</v>
+        <v>0.0401178898413</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1561,13 +1519,13 @@
         <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>1618945</v>
+        <v>1120591</v>
       </c>
       <c r="G15" s="15">
-        <v>15707.81</v>
+        <v>21937.81</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0319406464407</v>
+        <v>0.0398324439145</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1590,13 +1548,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>1027893</v>
+        <v>1369402</v>
       </c>
       <c r="G16" s="15">
-        <v>15672.80</v>
+        <v>21754.32</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0318694562473</v>
+        <v>0.0394992814369</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1616,16 +1574,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F17" s="14">
-        <v>568368</v>
+        <v>2097344</v>
       </c>
       <c r="G17" s="15">
-        <v>13842.03</v>
+        <v>13560.38</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0281467235885</v>
+        <v>0.024621558661</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1636,25 +1594,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F18" s="14">
-        <v>180445</v>
+        <v>222453</v>
       </c>
       <c r="G18" s="15">
-        <v>12289.21</v>
+        <v>12486.95</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0249891812827</v>
+        <v>0.0226725336548</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1677,13 +1635,13 @@
         <v>17</v>
       </c>
       <c r="F19" s="14">
-        <v>217231</v>
+        <v>1074403</v>
       </c>
       <c r="G19" s="15">
-        <v>9858.38</v>
+        <v>10937.96</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0200462718901</v>
+        <v>0.0198600351739</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1703,16 +1661,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F20" s="14">
-        <v>630652</v>
+        <v>143581</v>
       </c>
       <c r="G20" s="15">
-        <v>9356.35</v>
+        <v>9879.09</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0190254317645</v>
+        <v>0.0179374467347</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1723,25 +1681,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F21" s="14">
-        <v>127779</v>
+        <v>937074</v>
       </c>
       <c r="G21" s="15">
-        <v>9244.94</v>
+        <v>9055.88</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0187988879357</v>
+        <v>0.0164427457525</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1764,13 +1722,13 @@
         <v>17</v>
       </c>
       <c r="F22" s="14">
-        <v>2527067</v>
+        <v>361177</v>
       </c>
       <c r="G22" s="15">
-        <v>9161.88</v>
+        <v>8912.76</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0186299916928</v>
+        <v>0.0161828830144</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1793,13 +1751,13 @@
         <v>17</v>
       </c>
       <c r="F23" s="14">
-        <v>857651</v>
+        <v>2652542</v>
       </c>
       <c r="G23" s="15">
-        <v>8305.06</v>
+        <v>8908.56</v>
       </c>
       <c r="H23" s="16">
-        <v>0.016887712872</v>
+        <v>0.0161752570817</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1819,16 +1777,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F24" s="14">
-        <v>1003547</v>
+        <v>963149</v>
       </c>
       <c r="G24" s="15">
-        <v>7492.98</v>
+        <v>8681.83</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0152364094655</v>
+        <v>0.0157635838103</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1848,16 +1806,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F25" s="14">
-        <v>1269825</v>
+        <v>20000000</v>
       </c>
       <c r="G25" s="15">
-        <v>7314.83</v>
+        <v>7906</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0148741548824</v>
+        <v>0.0143549106127</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1868,25 +1826,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F26" s="14">
-        <v>996959</v>
+        <v>747955</v>
       </c>
       <c r="G26" s="15">
-        <v>7211.50</v>
+        <v>7847.54</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0146640411239</v>
+        <v>0.0142487648911</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1909,13 +1867,13 @@
         <v>17</v>
       </c>
       <c r="F27" s="14">
-        <v>2112383</v>
+        <v>2566479</v>
       </c>
       <c r="G27" s="15">
-        <v>6964.53</v>
+        <v>7830.33</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0141618462634</v>
+        <v>0.0142175167237</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1938,13 +1896,13 @@
         <v>17</v>
       </c>
       <c r="F28" s="14">
-        <v>963149</v>
+        <v>857651</v>
       </c>
       <c r="G28" s="15">
-        <v>6835.47</v>
+        <v>7824.78</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0138994124913</v>
+        <v>0.0142074395982</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1964,16 +1922,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F29" s="14">
-        <v>680770</v>
+        <v>1516671</v>
       </c>
       <c r="G29" s="15">
-        <v>6264.11</v>
+        <v>7512.83</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0127375950419</v>
+        <v>0.0136410325194</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -1984,25 +1942,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F30" s="14">
-        <v>749057</v>
+        <v>1589896</v>
       </c>
       <c r="G30" s="15">
-        <v>5979.35</v>
+        <v>7056.75</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0121585570678</v>
+        <v>0.0128129288472</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2013,25 +1971,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F31" s="14">
-        <v>1032567</v>
+        <v>150243</v>
       </c>
       <c r="G31" s="15">
-        <v>5677.57</v>
+        <v>7032.72</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0115449102078</v>
+        <v>0.0127692976175</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2042,25 +2000,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="F32" s="14">
-        <v>1197689</v>
+        <v>1465869</v>
       </c>
       <c r="G32" s="15">
-        <v>5629.14</v>
+        <v>7001.72</v>
       </c>
       <c r="H32" s="16">
-        <v>0.011446431457</v>
+        <v>0.0127130109708</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2071,25 +2029,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F33" s="14">
-        <v>123730</v>
+        <v>3436513</v>
       </c>
       <c r="G33" s="15">
-        <v>5511.99</v>
+        <v>6362.70</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0112082157713</v>
+        <v>0.011552743455</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2109,16 +2067,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F34" s="14">
-        <v>378822</v>
+        <v>1161925</v>
       </c>
       <c r="G34" s="15">
-        <v>5505.04</v>
+        <v>5876.44</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0111940834707</v>
+        <v>0.0106698420087</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2138,16 +2096,16 @@
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F35" s="14">
-        <v>1235374</v>
+        <v>105676</v>
       </c>
       <c r="G35" s="15">
-        <v>5493.71</v>
+        <v>5567.65</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0111710447705</v>
+        <v>0.0101091725364</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2170,13 +2128,13 @@
         <v>17</v>
       </c>
       <c r="F36" s="14">
-        <v>1337336</v>
+        <v>378822</v>
       </c>
       <c r="G36" s="15">
-        <v>5421.56</v>
+        <v>5519.82</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0110243331894</v>
+        <v>0.0100223276876</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2196,16 +2154,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F37" s="14">
-        <v>81191</v>
+        <v>1154584</v>
       </c>
       <c r="G37" s="15">
-        <v>5103.42</v>
+        <v>5417.89</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0103774195039</v>
+        <v>0.0098372535617</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2228,13 +2186,13 @@
         <v>17</v>
       </c>
       <c r="F38" s="14">
-        <v>676935</v>
+        <v>1197689</v>
       </c>
       <c r="G38" s="15">
-        <v>5080.06</v>
+        <v>5256.66</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0103299187065</v>
+        <v>0.0095445085278</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2254,16 +2212,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F39" s="14">
-        <v>1133400</v>
+        <v>78012</v>
       </c>
       <c r="G39" s="15">
-        <v>4837.35</v>
+        <v>4484.13</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0098363862346</v>
+        <v>0.0081418271345</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2283,16 +2241,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F40" s="14">
-        <v>750395</v>
+        <v>55021</v>
       </c>
       <c r="G40" s="15">
-        <v>4804.03</v>
+        <v>4386.27</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0097686325286</v>
+        <v>0.0079641429007</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2315,13 +2273,13 @@
         <v>17</v>
       </c>
       <c r="F41" s="14">
-        <v>97769</v>
+        <v>297612</v>
       </c>
       <c r="G41" s="15">
-        <v>4583.26</v>
+        <v>3957.94</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0093197133913</v>
+        <v>0.0071864248558</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2344,13 +2302,13 @@
         <v>17</v>
       </c>
       <c r="F42" s="14">
-        <v>78012</v>
+        <v>640883</v>
       </c>
       <c r="G42" s="15">
-        <v>4199.07</v>
+        <v>3353.42</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0085384920144</v>
+        <v>0.0060887989307</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2370,16 +2328,16 @@
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F43" s="14">
-        <v>891118</v>
+        <v>241030</v>
       </c>
       <c r="G43" s="15">
-        <v>3860.77</v>
+        <v>1441.84</v>
       </c>
       <c r="H43" s="16">
-        <v>0.00785058449</v>
+        <v>0.00261794641</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2399,16 +2357,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="F44" s="14">
-        <v>297612</v>
+        <v>202898</v>
       </c>
       <c r="G44" s="15">
-        <v>3656.16</v>
+        <v>778.62</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0074345254934</v>
+        <v>0.0014137389958</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2419,25 +2377,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F45" s="14">
-        <v>302205</v>
+        <v>25816</v>
       </c>
       <c r="G45" s="15">
-        <v>3627.22</v>
+        <v>52.66</v>
       </c>
       <c r="H45" s="16">
-        <v>0.007375678187</v>
+        <v>0.0000956146714</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2448,56 +2406,35 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="14">
-        <v>1720119</v>
-      </c>
-      <c r="G46" s="15">
-        <v>2750.47</v>
-      </c>
-      <c r="H46" s="16">
-        <v>0.005592873215</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F47" s="14">
-        <v>413334</v>
-      </c>
-      <c r="G47" s="15">
-        <v>2031.74</v>
-      </c>
-      <c r="H47" s="16">
-        <v>0.00413138999</v>
-      </c>
-      <c r="I47" s="15" t="s">
+      <c r="H47" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I47" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="11" t="s">
@@ -2506,27 +2443,6 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F48" s="14">
-        <v>407121</v>
-      </c>
-      <c r="G48" s="15">
-        <v>2011.38</v>
-      </c>
-      <c r="H48" s="16">
-        <v>0.0040899894662</v>
-      </c>
-      <c r="I48" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J48" s="11" t="s">
@@ -2534,28 +2450,28 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" s="14">
-        <v>270635</v>
-      </c>
-      <c r="G49" s="15">
-        <v>1912.58</v>
-      </c>
-      <c r="H49" s="16">
-        <v>0.0038890871209</v>
-      </c>
-      <c r="I49" s="15" t="s">
+      <c r="B49" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I49" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -2564,27 +2480,6 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F50" s="14">
-        <v>107573</v>
-      </c>
-      <c r="G50" s="15">
-        <v>1800.40</v>
-      </c>
-      <c r="H50" s="16">
-        <v>0.0036609775552</v>
-      </c>
-      <c r="I50" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -2592,28 +2487,28 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F51" s="14">
-        <v>24211</v>
-      </c>
-      <c r="G51" s="15">
-        <v>577.99</v>
-      </c>
-      <c r="H51" s="16">
-        <v>0.0011752990541</v>
-      </c>
-      <c r="I51" s="15" t="s">
+      <c r="B51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I51" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J51" s="11" t="s">
@@ -2622,471 +2517,464 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1">
+      <c r="B62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1">
+      <c r="B66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1">
+      <c r="B67" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="15" customHeight="1">
+      <c r="B68" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="15" customHeight="1">
+      <c r="B69" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="15" customHeight="1">
+      <c r="B70" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1">
+      <c r="B71" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1">
+      <c r="B72" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1">
+      <c r="B73" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F52" s="14">
-        <v>170593</v>
-      </c>
-      <c r="G52" s="15">
-        <v>370.65</v>
-      </c>
-      <c r="H52" s="16">
-        <v>0.0007536888085</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
+      <c r="C73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="9">
+        <v>15991.92</v>
+      </c>
+      <c r="H73" s="10">
+        <v>0.0290365016601</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9" t="s">
+      <c r="C75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="9">
+        <v>840.51924</v>
+      </c>
+      <c r="H75" s="10">
+        <v>0.0015261293395</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1">
+      <c r="B76" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="H54" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H60" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H62" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I64" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I66" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="15" customHeight="1">
-      <c r="B68" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I68" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" ht="15" customHeight="1">
-      <c r="B70" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I70" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" ht="15" customHeight="1">
-      <c r="B71" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I76" s="9" t="s">
+      <c r="C76" s="13"/>
+      <c r="D76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="13"/>
+      <c r="G76" s="15">
+        <v>840.51924</v>
+      </c>
+      <c r="H76" s="16">
+        <v>0.0015261293395</v>
+      </c>
+      <c r="I76" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J76" s="11" t="s">
@@ -3102,277 +2990,144 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="11" t="s">
+      <c r="B78" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="18">
+        <v>-243.02176470006816</v>
+      </c>
+      <c r="H78" s="19">
+        <v>-0.0004412542005073835</v>
+      </c>
+      <c r="I78" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="9">
-        <v>5325.08</v>
-      </c>
-      <c r="H80" s="10">
-        <v>0.0108281483891</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" s="9">
-        <v>840.51924</v>
-      </c>
-      <c r="H82" s="10">
-        <v>0.0017091324552</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="13"/>
-      <c r="G83" s="15">
-        <v>840.51924</v>
-      </c>
-      <c r="H83" s="16">
-        <v>0.0017091324552</v>
-      </c>
-      <c r="I83" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="18">
-        <v>-226.0315631099511</v>
-      </c>
-      <c r="H85" s="19">
-        <v>-0.00045961812892670966</v>
-      </c>
-      <c r="I85" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="18">
-        <v>491781.21767689</v>
-      </c>
-      <c r="H86" s="19">
-        <v>0.9999999999978733</v>
-      </c>
-      <c r="I86" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" ht="15" customHeight="1">
-      <c r="B89" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C89" s="21"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="21"/>
-      <c r="G89" s="21"/>
-      <c r="H89" s="21"/>
-      <c r="I89" s="21"/>
-    </row>
-    <row r="90" spans="2:8" ht="15" customHeight="1">
-      <c r="B90" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C90" s="21"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="21"/>
-      <c r="G90" s="21"/>
-      <c r="H90" s="21"/>
-    </row>
-    <row r="91" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B91" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="C91" s="21"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="21"/>
-      <c r="G91" s="21"/>
-      <c r="H91" s="21"/>
-    </row>
-    <row r="92" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B92" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="C92" s="21"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="21"/>
-      <c r="G92" s="21"/>
-      <c r="H92" s="21"/>
-    </row>
-    <row r="93" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B93" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C93" s="21"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="21"/>
-      <c r="G93" s="21"/>
-      <c r="H93" s="21"/>
-    </row>
-    <row r="96" ht="15">
-      <c r="B96" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="111" ht="15">
-      <c r="B111" s="21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="112" ht="15">
-      <c r="B112" s="21" t="s">
-        <v>137</v>
+      <c r="B79" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="18">
+        <v>550752.2974753</v>
+      </c>
+      <c r="H79" s="19">
+        <v>0.9999999999980927</v>
+      </c>
+      <c r="I79" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" ht="15" customHeight="1">
+      <c r="B82" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
+    </row>
+    <row r="83" spans="2:8" ht="15" customHeight="1">
+      <c r="B83" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+    </row>
+    <row r="84" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B84" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="21"/>
+    </row>
+    <row r="85" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B85" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="21"/>
+      <c r="H85" s="21"/>
+    </row>
+    <row r="86" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B86" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="21"/>
+      <c r="H86" s="21"/>
+    </row>
+    <row r="89" ht="15">
+      <c r="B89" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" ht="15">
+      <c r="B104" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105" ht="15">
+      <c r="B105" s="21" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B92:H92"/>
-    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B84:H84"/>
+    <mergeCell ref="B85:H85"/>
+    <mergeCell ref="B86:H86"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="B83:H83"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
